--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
         <v>110647</v>
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,53 +1121,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>110647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110647</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1014,48 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>110647</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B6" t="n">
         <v>110647</v>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>110647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>110647</v>
+        <v>58097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R12" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>58097</v>
+        <v>110647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R13" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2112,38 +2112,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,42 +2228,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129617357</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110647</v>
+        <v>110676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,53 +1014,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616503</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>110676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580694</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400829</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129620441</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
-        <v>110647</v>
+        <v>110676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580732</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400807</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616134</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110647</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580684</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400847</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
         <v>129617936</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110647</v>
+        <v>110676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B12" t="n">
-        <v>58097</v>
+        <v>110676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R12" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B13" t="n">
-        <v>110647</v>
+        <v>58100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R13" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,7 +2008,7 @@
         <v>129617269</v>
       </c>
       <c r="B14" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,6 +2453,1084 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129678798</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56911</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580682</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6400886</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Uppflog, ngt osäker men tyckte bullret var arttypiskt!</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129679908</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580736</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6400804</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129679888</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>580710</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6400826</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129679855</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>580682</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6400886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129679936</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>580747</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6400822</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129679800</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580657</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6400934</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129679791</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580667</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6400917</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129678940</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92004</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>580725</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6400844</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129679797</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>580677</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6400916</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129679808</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>580686</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6400878</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,6 +3532,115 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129679817</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92000</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>580682</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6400886</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På tall - tallkötticka</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129617357</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616134</v>
       </c>
       <c r="B5" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580684</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400847</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,48 +1121,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129616503</v>
       </c>
       <c r="B6" t="n">
-        <v>110676</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580694</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400829</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129620441</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>110688</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580732</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400807</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
         <v>129617936</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>129616552</v>
       </c>
       <c r="B12" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616677</v>
       </c>
       <c r="B13" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129617269</v>
       </c>
       <c r="B14" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129678798</v>
       </c>
       <c r="B18" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,42 +2676,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>57895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R20" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2775,53 +2778,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679855</v>
+        <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>57890</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2828,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R21" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,6 +2872,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>129679936</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3534,51 +3534,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129679817</v>
+        <v>129716635</v>
       </c>
       <c r="B28" t="n">
-        <v>92000</v>
+        <v>58105</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>103015</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580682</v>
+        <v>580602</v>
       </c>
       <c r="R28" t="n">
-        <v>6400886</v>
+        <v>6400630</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3605,17 +3599,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På tall - tallkötticka</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,22 +3623,245 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129716000</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>580679</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6400859</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129716919</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>580568</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6400615</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129617357</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,53 +1121,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>110689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110688</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
         <v>129617936</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>129616552</v>
       </c>
       <c r="B12" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616677</v>
       </c>
       <c r="B13" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129617269</v>
       </c>
       <c r="B14" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,38 +2112,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B15" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,42 +2228,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129678798</v>
       </c>
       <c r="B18" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>129679936</v>
       </c>
       <c r="B22" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129716635</v>
       </c>
       <c r="B28" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>129716000</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129716919</v>
       </c>
       <c r="B30" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1014,48 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>110689</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B6" t="n">
         <v>110689</v>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>110689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>110689</v>
+        <v>58106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R12" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>58106</v>
+        <v>110689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R13" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129620441</v>
       </c>
       <c r="B6" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,46 +2676,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2723,13 +2719,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R20" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,6 +2763,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,49 +2775,53 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,13 +2829,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R21" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2873,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92011</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2112,38 +2112,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,42 +2228,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2676,42 +2676,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R20" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2775,53 +2778,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2828,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R21" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,6 +2872,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1014,53 +1014,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616503</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>110694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580694</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400829</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129620441</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
         <v>110694</v>
@@ -1161,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580732</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400807</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616134</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110694</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580684</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400847</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B12" t="n">
-        <v>58106</v>
+        <v>110694</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R12" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B13" t="n">
-        <v>110694</v>
+        <v>58106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R13" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1014,48 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>110694</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B6" t="n">
         <v>110694</v>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>110694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>110694</v>
+        <v>58106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R12" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>58106</v>
+        <v>110694</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R13" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2676,46 +2676,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2723,13 +2719,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R20" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,6 +2763,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,49 +2775,53 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,13 +2829,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R21" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2873,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110694</v>
+        <v>110698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,53 +1014,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616503</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>110698</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580694</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400829</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129620441</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
-        <v>110694</v>
+        <v>110698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580732</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400807</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616134</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110694</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580684</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400847</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110694</v>
+        <v>110698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B12" t="n">
-        <v>58106</v>
+        <v>110698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R12" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B13" t="n">
-        <v>110694</v>
+        <v>58106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R13" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,38 +2112,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,42 +2228,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,42 +2676,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R20" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2775,53 +2778,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2828,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R21" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,6 +2872,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>92020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110698</v>
+        <v>110700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,48 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>110698</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B6" t="n">
-        <v>110698</v>
+        <v>110700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>110700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110698</v>
+        <v>110700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616552</v>
+        <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>110698</v>
+        <v>58106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580692</v>
+        <v>580709</v>
       </c>
       <c r="R12" t="n">
-        <v>6400823</v>
+        <v>6400795</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616677</v>
+        <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>58106</v>
+        <v>110700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580709</v>
+        <v>580692</v>
       </c>
       <c r="R13" t="n">
-        <v>6400795</v>
+        <v>6400823</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2112,38 +2112,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,42 +2228,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110700</v>
+        <v>110735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,53 +1014,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616503</v>
+        <v>129620441</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>110735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580694</v>
+        <v>580732</v>
       </c>
       <c r="R5" t="n">
-        <v>6400829</v>
+        <v>6400807</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129620441</v>
+        <v>129616134</v>
       </c>
       <c r="B6" t="n">
-        <v>110700</v>
+        <v>110735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580732</v>
+        <v>580684</v>
       </c>
       <c r="R6" t="n">
-        <v>6400807</v>
+        <v>6400847</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,48 +1228,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616134</v>
+        <v>129616503</v>
       </c>
       <c r="B7" t="n">
-        <v>110700</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580684</v>
+        <v>580694</v>
       </c>
       <c r="R7" t="n">
-        <v>6400847</v>
+        <v>6400829</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110700</v>
+        <v>110735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>110700</v>
+        <v>110735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,42 +2112,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616252</v>
+        <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580686</v>
+        <v>580724</v>
       </c>
       <c r="R15" t="n">
-        <v>6400843</v>
+        <v>6400808</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2191,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,38 +2224,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620476</v>
+        <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580724</v>
+        <v>580686</v>
       </c>
       <c r="R16" t="n">
-        <v>6400808</v>
+        <v>6400843</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129617357</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,48 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620441</v>
+        <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>110735</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580732</v>
+        <v>580694</v>
       </c>
       <c r="R5" t="n">
-        <v>6400807</v>
+        <v>6400829</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616134</v>
+        <v>129620441</v>
       </c>
       <c r="B6" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R6" t="n">
-        <v>6400847</v>
+        <v>6400807</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616503</v>
+        <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>110739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580694</v>
+        <v>580684</v>
       </c>
       <c r="R7" t="n">
-        <v>6400829</v>
+        <v>6400847</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
         <v>129617936</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129617269</v>
       </c>
       <c r="B14" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129678798</v>
       </c>
       <c r="B18" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>129679936</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92022</v>
+        <v>92025</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129716635</v>
       </c>
       <c r="B28" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>129716000</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129716919</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616666</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129617357</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129620499</v>
       </c>
       <c r="B4" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129616503</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129620441</v>
       </c>
       <c r="B6" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129616134</v>
       </c>
       <c r="B7" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129617936</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129617462</v>
       </c>
       <c r="B9" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>129616302</v>
       </c>
       <c r="B10" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129617115</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>129616677</v>
       </c>
       <c r="B12" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129616552</v>
       </c>
       <c r="B13" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129617269</v>
       </c>
       <c r="B14" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>129620476</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129616252</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129616400</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129678798</v>
       </c>
       <c r="B18" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>129679936</v>
       </c>
       <c r="B22" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92025</v>
+        <v>92028</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129716635</v>
       </c>
       <c r="B28" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>129716000</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129716919</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,46 +2676,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2723,13 +2719,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R20" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,6 +2763,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,49 +2775,53 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,13 +2829,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R21" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2873,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2676,42 +2676,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>98798</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R20" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2775,53 +2778,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2828,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R21" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,6 +2872,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2676,46 +2676,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2723,13 +2719,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R20" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,6 +2763,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,49 +2775,53 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,13 +2829,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R21" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2873,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2569,7 +2569,7 @@
         <v>129679908</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,42 +2676,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129679888</v>
+        <v>129678786</v>
       </c>
       <c r="B20" t="n">
-        <v>98798</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580710</v>
+        <v>580682</v>
       </c>
       <c r="R20" t="n">
-        <v>6400826</v>
+        <v>6400886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2775,53 +2778,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678786</v>
+        <v>129679888</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2828,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580682</v>
+        <v>580710</v>
       </c>
       <c r="R21" t="n">
-        <v>6400886</v>
+        <v>6400826</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,6 +2872,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>129679800</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129679791</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129678940</v>
       </c>
       <c r="B25" t="n">
-        <v>92029</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>129679808</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129716635</v>
       </c>
       <c r="B28" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>129716000</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129616666</v>
+        <v>129678940</v>
       </c>
       <c r="B2" t="n">
-        <v>100986</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580709</v>
+        <v>580725</v>
       </c>
       <c r="R2" t="n">
-        <v>6400795</v>
+        <v>6400844</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,75 +770,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129617357</v>
+        <v>129616503</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580613</v>
+        <v>580694</v>
       </c>
       <c r="R3" t="n">
-        <v>6400571</v>
+        <v>6400829</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129620499</v>
+        <v>129617936</v>
       </c>
       <c r="B4" t="n">
-        <v>110742</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +912,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580735</v>
+        <v>580617</v>
       </c>
       <c r="R4" t="n">
-        <v>6400802</v>
+        <v>6400527</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,14 +1013,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616503</v>
+        <v>129620476</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1054,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580694</v>
+        <v>580724</v>
       </c>
       <c r="R5" t="n">
-        <v>6400829</v>
+        <v>6400808</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1089,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129620441</v>
+        <v>129678927</v>
       </c>
       <c r="B6" t="n">
-        <v>110742</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,37 +1136,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580732</v>
+        <v>580747</v>
       </c>
       <c r="R6" t="n">
-        <v>6400807</v>
+        <v>6400822</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129616134</v>
+        <v>129716919</v>
       </c>
       <c r="B7" t="n">
-        <v>110742</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,37 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580684</v>
+        <v>580568</v>
       </c>
       <c r="R7" t="n">
-        <v>6400847</v>
+        <v>6400615</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,22 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,27 +1342,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129617936</v>
+        <v>129678798</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,71 +1370,69 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580617</v>
+        <v>580682</v>
       </c>
       <c r="R8" t="n">
-        <v>6400527</v>
+        <v>6400886</v>
       </c>
       <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppflog, ngt osäker men tyckte bullret var arttypiskt!</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
         <v>1</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1440,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129617462</v>
+        <v>129616677</v>
       </c>
       <c r="B9" t="n">
-        <v>100986</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,37 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580609</v>
+        <v>580709</v>
       </c>
       <c r="R9" t="n">
-        <v>6400573</v>
+        <v>6400795</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129616302</v>
+        <v>129617269</v>
       </c>
       <c r="B10" t="n">
-        <v>110742</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,46 +1570,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580685</v>
+        <v>580623</v>
       </c>
       <c r="R10" t="n">
-        <v>6400840</v>
+        <v>6400588</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,57 +1666,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617115</v>
+        <v>129716635</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580616</v>
+        <v>580602</v>
       </c>
       <c r="R11" t="n">
-        <v>6400632</v>
+        <v>6400630</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,22 +1731,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,45 +1773,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616677</v>
+        <v>129617357</v>
       </c>
       <c r="B12" t="n">
-        <v>58111</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580709</v>
+        <v>580613</v>
       </c>
       <c r="R12" t="n">
-        <v>6400795</v>
+        <v>6400571</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1861,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,48 +1889,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616552</v>
+        <v>129678786</v>
       </c>
       <c r="B13" t="n">
-        <v>110742</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580692</v>
+        <v>580682</v>
       </c>
       <c r="R13" t="n">
-        <v>6400823</v>
+        <v>6400886</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,22 +1966,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,57 +1986,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617269</v>
+        <v>129716000</v>
       </c>
       <c r="B14" t="n">
-        <v>58111</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580623</v>
+        <v>580679</v>
       </c>
       <c r="R14" t="n">
-        <v>6400588</v>
+        <v>6400859</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,22 +2068,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,53 +2110,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620476</v>
+        <v>129616134</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>111175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580724</v>
+        <v>580684</v>
       </c>
       <c r="R15" t="n">
-        <v>6400808</v>
+        <v>6400847</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,37 +2217,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616252</v>
+        <v>129616302</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>111175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580686</v>
+        <v>580685</v>
       </c>
       <c r="R16" t="n">
-        <v>6400843</v>
+        <v>6400840</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2303,7 +2296,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2306,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,57 +2333,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129616400</v>
+        <v>129616552</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>111175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580691</v>
+        <v>580692</v>
       </c>
       <c r="R17" t="n">
-        <v>6400838</v>
+        <v>6400823</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2419,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2429,7 +2413,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,56 +2440,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678798</v>
+        <v>129620441</v>
       </c>
       <c r="B18" t="n">
-        <v>56921</v>
+        <v>111175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>219677</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580682</v>
+        <v>580732</v>
       </c>
       <c r="R18" t="n">
-        <v>6400886</v>
+        <v>6400807</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,24 +2505,29 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppflog, ngt osäker men tyckte bullret var arttypiskt!</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2554,72 +2535,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129679908</v>
+        <v>129620499</v>
       </c>
       <c r="B19" t="n">
-        <v>98815</v>
+        <v>111175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580736</v>
+        <v>580735</v>
       </c>
       <c r="R19" t="n">
-        <v>6400804</v>
+        <v>6400802</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2643,12 +2612,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,79 +2636,75 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678786</v>
+        <v>129616252</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580682</v>
+        <v>580686</v>
       </c>
       <c r="R20" t="n">
-        <v>6400886</v>
+        <v>6400843</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,12 +2728,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,22 +2758,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129679888</v>
+        <v>129616400</v>
       </c>
       <c r="B21" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,28 +2798,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580710</v>
+        <v>580691</v>
       </c>
       <c r="R21" t="n">
-        <v>6400826</v>
+        <v>6400838</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,12 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,75 +2868,75 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129679936</v>
+        <v>129617115</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580747</v>
+        <v>580616</v>
       </c>
       <c r="R22" t="n">
-        <v>6400822</v>
+        <v>6400632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,12 +2960,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,22 +2990,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129679800</v>
+        <v>129678855</v>
       </c>
       <c r="B23" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580657</v>
+        <v>580710</v>
       </c>
       <c r="R23" t="n">
-        <v>6400934</v>
+        <v>6400826</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,17 +3101,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129679791</v>
+        <v>129678892</v>
       </c>
       <c r="B24" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,7 +3136,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3145,10 +3155,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580667</v>
+        <v>580736</v>
       </c>
       <c r="R24" t="n">
-        <v>6400917</v>
+        <v>6400804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3201,52 +3211,49 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678940</v>
+        <v>129679791</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3254,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580725</v>
+        <v>580667</v>
       </c>
       <c r="R25" t="n">
-        <v>6400844</v>
+        <v>6400917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3292,11 +3299,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3315,7 +3317,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3325,7 +3327,7 @@
         <v>129679797</v>
       </c>
       <c r="B26" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,10 +3430,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129679808</v>
+        <v>129679800</v>
       </c>
       <c r="B27" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3471,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580686</v>
+        <v>580657</v>
       </c>
       <c r="R27" t="n">
-        <v>6400878</v>
+        <v>6400934</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,48 +3536,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129716635</v>
+        <v>129679808</v>
       </c>
       <c r="B28" t="n">
-        <v>58112</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580602</v>
+        <v>580686</v>
       </c>
       <c r="R28" t="n">
-        <v>6400630</v>
+        <v>6400878</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3599,22 +3609,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,56 +3623,61 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129716000</v>
+        <v>129616666</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3681,13 +3686,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580679</v>
+        <v>580709</v>
       </c>
       <c r="R29" t="n">
-        <v>6400859</v>
+        <v>6400795</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,22 +3716,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,50 +3758,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129716919</v>
+        <v>129617462</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>101325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580568</v>
+        <v>580609</v>
       </c>
       <c r="R30" t="n">
-        <v>6400615</v>
+        <v>6400573</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3823,22 +3823,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
